--- a/src/main/resources/universityInfoStatistics.xlsx
+++ b/src/main/resources/universityInfoStatistics.xlsx
@@ -29,6 +29,12 @@
     <t>Количество университетов по профилю</t>
   </si>
   <si>
+    <t>Математика</t>
+  </si>
+  <si>
+    <t>Казанский Университет Вычислений;</t>
+  </si>
+  <si>
     <t>Медицина</t>
   </si>
   <si>
@@ -45,12 +51,6 @@
   </si>
   <si>
     <t>Московский Выдуманный Университет;Московский Придуманный Институт;</t>
-  </si>
-  <si>
-    <t>Математика</t>
-  </si>
-  <si>
-    <t>Казанский Университет Вычислений;</t>
   </si>
 </sst>
 </file>
@@ -133,16 +133,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>4.329999923706055</v>
+        <v>0.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>6</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="3">
@@ -150,16 +150,16 @@
         <v>7</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>0.0</v>
+        <v>4.329999923706055</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="4">
@@ -167,16 +167,16 @@
         <v>9</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>4.539999961853027</v>
+        <v>0.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>10</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="5">
@@ -184,16 +184,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>0.0</v>
+        <v>4.539999961853027</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>12</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/universityInfoStatistics.xlsx
+++ b/src/main/resources/universityInfoStatistics.xlsx
@@ -35,22 +35,22 @@
     <t>Казанский Университет Вычислений;</t>
   </si>
   <si>
+    <t>Физика</t>
+  </si>
+  <si>
+    <t>Московский Выдуманный Университет;Московский Придуманный Институт;</t>
+  </si>
+  <si>
+    <t>Лингвистика</t>
+  </si>
+  <si>
+    <t>Воронежский Литературно-Переводческий Университет;</t>
+  </si>
+  <si>
     <t>Медицина</t>
   </si>
   <si>
     <t>Московский Государственный Медицинский Университет;Тамбовский Университет Медицины;Самарский Медицинский Институт;</t>
-  </si>
-  <si>
-    <t>Лингвистика</t>
-  </si>
-  <si>
-    <t>Воронежский Литературно-Переводческий Университет;</t>
-  </si>
-  <si>
-    <t>Физика</t>
-  </si>
-  <si>
-    <t>Московский Выдуманный Университет;Московский Придуманный Институт;</t>
   </si>
 </sst>
 </file>
@@ -150,16 +150,16 @@
         <v>7</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>4.329999923706055</v>
+        <v>4.539999961853027</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="4">
@@ -184,16 +184,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>4.539999961853027</v>
+        <v>4.329999923706055</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>12</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/universityInfoStatistics.xlsx
+++ b/src/main/resources/universityInfoStatistics.xlsx
@@ -29,28 +29,28 @@
     <t>Количество университетов по профилю</t>
   </si>
   <si>
+    <t>Лингвистика</t>
+  </si>
+  <si>
+    <t>Воронежский Литературно-Переводческий Университет;</t>
+  </si>
+  <si>
     <t>Математика</t>
   </si>
   <si>
     <t>Казанский Университет Вычислений;</t>
   </si>
   <si>
+    <t>Медицина</t>
+  </si>
+  <si>
+    <t>Московский Государственный Медицинский Университет;Тамбовский Университет Медицины;Самарский Медицинский Институт;</t>
+  </si>
+  <si>
     <t>Физика</t>
   </si>
   <si>
     <t>Московский Выдуманный Университет;Московский Придуманный Институт;</t>
-  </si>
-  <si>
-    <t>Лингвистика</t>
-  </si>
-  <si>
-    <t>Воронежский Литературно-Переводческий Университет;</t>
-  </si>
-  <si>
-    <t>Медицина</t>
-  </si>
-  <si>
-    <t>Московский Государственный Медицинский Университет;Тамбовский Университет Медицины;Самарский Медицинский Институт;</t>
   </si>
 </sst>
 </file>
@@ -150,16 +150,16 @@
         <v>7</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>4.539999961853027</v>
+        <v>0.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>8</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="4">
@@ -167,16 +167,16 @@
         <v>9</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>0.0</v>
+        <v>4.329999923706055</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>10</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="5">
@@ -184,16 +184,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>4.329999923706055</v>
+        <v>4.539999961853027</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>12</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>
